--- a/MAR_ORIGINAL_Proyeccion_Produccion.xlsx
+++ b/MAR_ORIGINAL_Proyeccion_Produccion.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="196">
   <si>
     <t>MAR ORIGINAL — PROYECCIÓN DE PRODUCCIÓN · CAB / DAMA / KIDS</t>
   </si>
@@ -280,9 +280,6 @@
     <t>14</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>MAR ORIGINAL — CANTIDADES POR COLOR (colores activos para producción)</t>
   </si>
   <si>
@@ -292,39 +289,39 @@
     <t>Color</t>
   </si>
   <si>
+    <t>Blanco</t>
+  </si>
+  <si>
     <t>Negro</t>
   </si>
   <si>
-    <t>Blanco</t>
+    <t>Azul Rey</t>
   </si>
   <si>
     <t>Azul Marino</t>
   </si>
   <si>
-    <t>Azul Rey</t>
-  </si>
-  <si>
     <t>Verde Militar</t>
   </si>
   <si>
     <t>Azul Lavanda</t>
   </si>
   <si>
-    <t>Gris</t>
+    <t>Gris Claro</t>
+  </si>
+  <si>
+    <t>Vinotinto</t>
   </si>
   <si>
     <t>Aguamarina</t>
   </si>
   <si>
-    <t>Vinotinto</t>
+    <t>Amarillo Neón</t>
   </si>
   <si>
     <t>Rojo</t>
   </si>
   <si>
-    <t>Amarillo Neón</t>
-  </si>
-  <si>
     <t>DAMA — CANTIDADES POR COLOR</t>
   </si>
   <si>
@@ -352,16 +349,22 @@
     <t>Total</t>
   </si>
   <si>
+    <t>Blanco — Mín</t>
+  </si>
+  <si>
+    <t>Blanco — Máx</t>
+  </si>
+  <si>
     <t>Negro — Mín</t>
   </si>
   <si>
     <t>Negro — Máx</t>
   </si>
   <si>
-    <t>Blanco — Mín</t>
-  </si>
-  <si>
-    <t>Blanco — Máx</t>
+    <t>Azul Rey — Mín</t>
+  </si>
+  <si>
+    <t>Azul Rey — Máx</t>
   </si>
   <si>
     <t>Azul Marino — Mín</t>
@@ -370,12 +373,6 @@
     <t>Azul Marino — Máx</t>
   </si>
   <si>
-    <t>Azul Rey — Mín</t>
-  </si>
-  <si>
-    <t>Azul Rey — Máx</t>
-  </si>
-  <si>
     <t>Verde Militar — Mín</t>
   </si>
   <si>
@@ -388,10 +385,16 @@
     <t>Azul Lavanda — Máx</t>
   </si>
   <si>
-    <t>Gris — Mín</t>
-  </si>
-  <si>
-    <t>Gris — Máx</t>
+    <t>Gris Claro — Mín</t>
+  </si>
+  <si>
+    <t>Gris Claro — Máx</t>
+  </si>
+  <si>
+    <t>Vinotinto — Mín</t>
+  </si>
+  <si>
+    <t>Vinotinto — Máx</t>
   </si>
   <si>
     <t>Aguamarina — Mín</t>
@@ -400,10 +403,10 @@
     <t>Aguamarina — Máx</t>
   </si>
   <si>
-    <t>Vinotinto — Mín</t>
-  </si>
-  <si>
-    <t>Vinotinto — Máx</t>
+    <t>Amarillo Neón — Mín</t>
+  </si>
+  <si>
+    <t>Amarillo Neón — Máx</t>
   </si>
   <si>
     <t>Rojo — Mín</t>
@@ -412,12 +415,6 @@
     <t>Rojo — Máx</t>
   </si>
   <si>
-    <t>Amarillo Neón — Mín</t>
-  </si>
-  <si>
-    <t>Amarillo Neón — Máx</t>
-  </si>
-  <si>
     <t>DAMA — PRODUCCIÓN COLOR × TALLA</t>
   </si>
   <si>
@@ -496,7 +493,7 @@
     <t>★ = tienda con velocidad proyectada/ajustada</t>
   </si>
   <si>
-    <t>CABALLERO · 2650 – 2834 und</t>
+    <t>CABALLERO · 2650 – 2837 und</t>
   </si>
   <si>
     <t>Tot</t>
@@ -535,10 +532,10 @@
     <t>Vel. mensual proy.</t>
   </si>
   <si>
-    <t>DAMA · 2450 – 2626 und</t>
-  </si>
-  <si>
-    <t>KIDS · 2950 – 3180 und</t>
+    <t>DAMA · 2450 – 2629 und</t>
+  </si>
+  <si>
+    <t>KIDS · 2950 – 3172 und</t>
   </si>
   <si>
     <t>METODOLOGÍA — MAR ORIGINAL · PROYECCIÓN DE PRODUCCIÓN (CAB / DAMA / KIDS)</t>
@@ -1391,7 +1388,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="10">
-        <v>2834</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1639,7 +1636,7 @@
         <v>35</v>
       </c>
       <c r="B60" s="10">
-        <v>2626</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -1887,7 +1884,7 @@
         <v>35</v>
       </c>
       <c r="B84" s="10">
-        <v>3180</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -1947,7 +1944,7 @@
         <v>2650</v>
       </c>
       <c r="F89">
-        <v>2834</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -1967,7 +1964,7 @@
         <v>2450</v>
       </c>
       <c r="F90">
-        <v>2626</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -1987,7 +1984,7 @@
         <v>2950</v>
       </c>
       <c r="F91">
-        <v>3180</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -2007,7 +2004,7 @@
         <v>8050</v>
       </c>
       <c r="F92" s="11">
-        <v>8640</v>
+        <v>8638</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -2237,7 +2234,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2269,13 +2266,13 @@
         <v>70</v>
       </c>
       <c r="B5" s="8">
-        <v>0.162</v>
+        <v>0.17</v>
       </c>
       <c r="C5" s="9">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="D5" s="9">
-        <v>461</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2283,13 +2280,13 @@
         <v>71</v>
       </c>
       <c r="B6" s="8">
-        <v>0.302</v>
+        <v>0.286</v>
       </c>
       <c r="C6" s="9">
-        <v>801</v>
+        <v>758</v>
       </c>
       <c r="D6" s="9">
-        <v>854</v>
+        <v>810</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2297,13 +2294,13 @@
         <v>72</v>
       </c>
       <c r="B7" s="8">
-        <v>0.3</v>
+        <v>0.302</v>
       </c>
       <c r="C7" s="9">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="D7" s="9">
-        <v>848</v>
+        <v>856</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2311,13 +2308,13 @@
         <v>73</v>
       </c>
       <c r="B8" s="8">
-        <v>0.157</v>
+        <v>0.18</v>
       </c>
       <c r="C8" s="9">
-        <v>417</v>
+        <v>478</v>
       </c>
       <c r="D8" s="9">
-        <v>447</v>
+        <v>511</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2325,13 +2322,13 @@
         <v>74</v>
       </c>
       <c r="B9" s="8">
-        <v>0.078</v>
+        <v>0.061</v>
       </c>
       <c r="C9" s="9">
-        <v>207</v>
+        <v>162</v>
       </c>
       <c r="D9" s="9">
-        <v>224</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2345,7 +2342,7 @@
         <v>2650</v>
       </c>
       <c r="D10" s="9">
-        <v>2834</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2372,13 +2369,13 @@
         <v>77</v>
       </c>
       <c r="B14" s="8">
-        <v>0.168</v>
+        <v>0.187</v>
       </c>
       <c r="C14" s="9">
-        <v>412</v>
+        <v>459</v>
       </c>
       <c r="D14" s="9">
-        <v>442</v>
+        <v>493</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2386,13 +2383,13 @@
         <v>70</v>
       </c>
       <c r="B15" s="8">
-        <v>0.285</v>
+        <v>0.276</v>
       </c>
       <c r="C15" s="9">
-        <v>699</v>
+        <v>675</v>
       </c>
       <c r="D15" s="9">
-        <v>748</v>
+        <v>721</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2400,13 +2397,13 @@
         <v>71</v>
       </c>
       <c r="B16" s="8">
-        <v>0.29</v>
+        <v>0.282</v>
       </c>
       <c r="C16" s="9">
-        <v>710</v>
+        <v>690</v>
       </c>
       <c r="D16" s="9">
-        <v>758</v>
+        <v>739</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2428,13 +2425,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="8">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="C18" s="9">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D18" s="9">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2448,7 +2445,7 @@
         <v>2450</v>
       </c>
       <c r="D19" s="9">
-        <v>2626</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2475,13 +2472,13 @@
         <v>79</v>
       </c>
       <c r="B23" s="8">
-        <v>0.107</v>
+        <v>0.119</v>
       </c>
       <c r="C23" s="9">
-        <v>316</v>
+        <v>350</v>
       </c>
       <c r="D23" s="9">
-        <v>340</v>
+        <v>378</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2489,13 +2486,13 @@
         <v>80</v>
       </c>
       <c r="B24" s="8">
-        <v>0.118</v>
+        <v>0.116</v>
       </c>
       <c r="C24" s="9">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D24" s="9">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2503,13 +2500,13 @@
         <v>81</v>
       </c>
       <c r="B25" s="8">
-        <v>0.155</v>
+        <v>0.158</v>
       </c>
       <c r="C25" s="9">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="D25" s="9">
-        <v>490</v>
+        <v>500</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2517,13 +2514,13 @@
         <v>82</v>
       </c>
       <c r="B26" s="8">
-        <v>0.142</v>
+        <v>0.145</v>
       </c>
       <c r="C26" s="9">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="D26" s="9">
-        <v>452</v>
+        <v>460</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2531,13 +2528,13 @@
         <v>83</v>
       </c>
       <c r="B27" s="8">
-        <v>0.135</v>
+        <v>0.142</v>
       </c>
       <c r="C27" s="9">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="D27" s="9">
-        <v>428</v>
+        <v>451</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2545,13 +2542,13 @@
         <v>84</v>
       </c>
       <c r="B28" s="8">
-        <v>0.179</v>
+        <v>0.159</v>
       </c>
       <c r="C28" s="9">
-        <v>528</v>
+        <v>468</v>
       </c>
       <c r="D28" s="9">
-        <v>566</v>
+        <v>502</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2559,41 +2556,27 @@
         <v>85</v>
       </c>
       <c r="B29" s="8">
-        <v>0.133</v>
+        <v>0.162</v>
       </c>
       <c r="C29" s="9">
-        <v>393</v>
+        <v>478</v>
       </c>
       <c r="D29" s="9">
-        <v>424</v>
+        <v>512</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" t="s">
-        <v>86</v>
+      <c r="A30" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="B30" s="8">
-        <v>0.032</v>
+        <v>1</v>
       </c>
       <c r="C30" s="9">
-        <v>94</v>
+        <v>2950</v>
       </c>
       <c r="D30" s="9">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B31" s="8">
-        <v>1</v>
-      </c>
-      <c r="C31" s="9">
-        <v>2950</v>
-      </c>
-      <c r="D31" s="9">
-        <v>3180</v>
+        <v>3172</v>
       </c>
     </row>
   </sheetData>
@@ -2608,17 +2591,17 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>67</v>
@@ -2632,156 +2615,156 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B5" s="8">
-        <v>0.1886792452830189</v>
+        <v>0.1874208526804559</v>
       </c>
       <c r="C5" s="9">
-        <v>500</v>
+        <v>532</v>
       </c>
       <c r="D5" s="9">
-        <v>532</v>
+        <v>567</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B6" s="8">
-        <v>0.1637735849056604</v>
+        <v>0.1794005909666526</v>
       </c>
       <c r="C6" s="9">
-        <v>434</v>
+        <v>514</v>
       </c>
       <c r="D6" s="9">
-        <v>462</v>
+        <v>547</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B7" s="8">
-        <v>0.1626415094339623</v>
+        <v>0.1473195441114394</v>
       </c>
       <c r="C7" s="9">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="D7" s="9">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B8" s="8">
-        <v>0.1037735849056604</v>
+        <v>0.1274799493457155</v>
       </c>
       <c r="C8" s="9">
-        <v>275</v>
+        <v>367</v>
       </c>
       <c r="D8" s="9">
-        <v>294</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B9" s="8">
-        <v>0.1173584905660377</v>
+        <v>0.1042634022794428</v>
       </c>
       <c r="C9" s="9">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="D9" s="9">
-        <v>331</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B10" s="8">
-        <v>0.08754716981132075</v>
+        <v>0.07133811734909244</v>
       </c>
       <c r="C10" s="9">
-        <v>232</v>
+        <v>141</v>
       </c>
       <c r="D10" s="9">
-        <v>249</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B11" s="8">
-        <v>0.04867924528301887</v>
+        <v>0.05614183199662305</v>
       </c>
       <c r="C11" s="9">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D11" s="9">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B12" s="8">
-        <v>0.04528301886792453</v>
+        <v>0.03841283241874208</v>
       </c>
       <c r="C12" s="9">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="D12" s="9">
-        <v>130</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="8">
+        <v>0.03799071338117349</v>
+      </c>
+      <c r="C13" s="9">
+        <v>90</v>
+      </c>
+      <c r="D13" s="9">
         <v>98</v>
-      </c>
-      <c r="B13" s="8">
-        <v>0.03433962264150944</v>
-      </c>
-      <c r="C13" s="9">
-        <v>91</v>
-      </c>
-      <c r="D13" s="9">
-        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B14" s="8">
-        <v>0.0339622641509434</v>
+        <v>0.02532714225411566</v>
       </c>
       <c r="C14" s="9">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="D14" s="9">
-        <v>98</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B15" s="8">
-        <v>0.0139622641509434</v>
+        <v>0.02490502321654707</v>
       </c>
       <c r="C15" s="9">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D15" s="9">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2795,17 +2778,17 @@
         <v>2650</v>
       </c>
       <c r="D16" s="11">
-        <v>2834</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>67</v>
@@ -2819,16 +2802,16 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B20" s="8">
-        <v>0.1804081632653061</v>
+        <v>0.2039355992844365</v>
       </c>
       <c r="C20" s="9">
-        <v>442</v>
+        <v>551</v>
       </c>
       <c r="D20" s="9">
-        <v>471</v>
+        <v>587</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2836,13 +2819,13 @@
         <v>90</v>
       </c>
       <c r="B21" s="8">
-        <v>0.1616326530612245</v>
+        <v>0.1544424567680382</v>
       </c>
       <c r="C21" s="9">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="D21" s="9">
-        <v>422</v>
+        <v>443</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2850,97 +2833,97 @@
         <v>92</v>
       </c>
       <c r="B22" s="8">
-        <v>0.1579591836734694</v>
+        <v>0.1085271317829457</v>
       </c>
       <c r="C22" s="9">
-        <v>387</v>
+        <v>293</v>
       </c>
       <c r="D22" s="9">
-        <v>413</v>
+        <v>313</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B23" s="8">
-        <v>0.1028571428571429</v>
+        <v>0.09600477042337507</v>
       </c>
       <c r="C23" s="9">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D23" s="9">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B24" s="8">
-        <v>0.08897959183673469</v>
+        <v>0.0763267740011926</v>
       </c>
       <c r="C24" s="9">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="D24" s="9">
-        <v>233</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B25" s="8">
-        <v>0.05591836734693877</v>
+        <v>0.0626118067978533</v>
       </c>
       <c r="C25" s="9">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="D25" s="9">
-        <v>147</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B26" s="8">
-        <v>0.05346938775510204</v>
+        <v>0.06201550387596899</v>
       </c>
       <c r="C26" s="9">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D26" s="9">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B27" s="8">
-        <v>0.05142857142857143</v>
+        <v>0.05664877757901014</v>
       </c>
       <c r="C27" s="9">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D27" s="9">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B28" s="8">
-        <v>0.05102040816326531</v>
+        <v>0.05545617173524151</v>
       </c>
       <c r="C28" s="9">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D28" s="9">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2948,41 +2931,41 @@
         <v>97</v>
       </c>
       <c r="B29" s="8">
-        <v>0.04979591836734694</v>
+        <v>0.04710793082886106</v>
       </c>
       <c r="C29" s="9">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D29" s="9">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B30" s="8">
-        <v>0.02938775510204081</v>
+        <v>0.04174120453190221</v>
       </c>
       <c r="C30" s="9">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D30" s="9">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B31" s="8">
-        <v>0.01714285714285714</v>
+        <v>0.03518187239117471</v>
       </c>
       <c r="C31" s="9">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D31" s="9">
-        <v>47</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2996,17 +2979,17 @@
         <v>2450</v>
       </c>
       <c r="D32" s="11">
-        <v>2626</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>67</v>
@@ -3023,69 +3006,69 @@
         <v>91</v>
       </c>
       <c r="B36" s="8">
-        <v>0.1654237288135593</v>
+        <v>0.1317829457364341</v>
       </c>
       <c r="C36" s="9">
-        <v>488</v>
+        <v>409</v>
       </c>
       <c r="D36" s="9">
-        <v>521</v>
+        <v>437</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B37" s="8">
-        <v>0.1471186440677966</v>
+        <v>0.1309216192937123</v>
       </c>
       <c r="C37" s="9">
-        <v>434</v>
+        <v>405</v>
       </c>
       <c r="D37" s="9">
-        <v>464</v>
+        <v>433</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B38" s="8">
-        <v>0.1369491525423729</v>
+        <v>0.1188630490956072</v>
       </c>
       <c r="C38" s="9">
-        <v>404</v>
+        <v>368</v>
       </c>
       <c r="D38" s="9">
-        <v>431</v>
+        <v>394</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B39" s="8">
-        <v>0.06338983050847458</v>
+        <v>0.1076658053402239</v>
       </c>
       <c r="C39" s="9">
-        <v>187</v>
+        <v>334</v>
       </c>
       <c r="D39" s="9">
-        <v>203</v>
+        <v>359</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B40" s="8">
-        <v>0.09186440677966101</v>
+        <v>0.09991386735572783</v>
       </c>
       <c r="C40" s="9">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="D40" s="9">
-        <v>292</v>
+        <v>331</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3093,97 +3076,97 @@
         <v>97</v>
       </c>
       <c r="B41" s="8">
-        <v>0.07661016949152542</v>
+        <v>0.08699397071490095</v>
       </c>
       <c r="C41" s="9">
-        <v>226</v>
+        <v>269</v>
       </c>
       <c r="D41" s="9">
-        <v>244</v>
+        <v>288</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B42" s="8">
-        <v>0.06474576271186441</v>
+        <v>0.08527131782945736</v>
       </c>
       <c r="C42" s="9">
-        <v>191</v>
+        <v>265</v>
       </c>
       <c r="D42" s="9">
-        <v>208</v>
+        <v>284</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B43" s="8">
-        <v>0.06508474576271187</v>
+        <v>0.06546080964685616</v>
       </c>
       <c r="C43" s="9">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D43" s="9">
-        <v>208</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B44" s="8">
-        <v>0.06203389830508475</v>
+        <v>0.06459948320413436</v>
       </c>
       <c r="C44" s="9">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="D44" s="9">
-        <v>198</v>
+        <v>180</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B45" s="8">
-        <v>0.05694915254237288</v>
+        <v>0.05254091300602928</v>
       </c>
       <c r="C45" s="9">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="D45" s="9">
-        <v>183</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B46" s="8">
-        <v>0.03932203389830508</v>
+        <v>0.03359173126614987</v>
       </c>
       <c r="C46" s="9">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="D46" s="9">
-        <v>128</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B47" s="8">
-        <v>0.03050847457627119</v>
+        <v>0.02239448751076658</v>
       </c>
       <c r="C47" s="9">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="D47" s="9">
-        <v>100</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3197,7 +3180,7 @@
         <v>2950</v>
       </c>
       <c r="D48" s="11">
-        <v>3180</v>
+        <v>3172</v>
       </c>
     </row>
   </sheetData>
@@ -3207,22 +3190,22 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>70</v>
@@ -3240,523 +3223,523 @@
         <v>74</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B5">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="C5">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="D5">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E5">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="F5">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>500</v>
+        <v>532</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="C6">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D6">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E6">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="F6">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>532</v>
+        <v>567</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B7">
         <v>79</v>
       </c>
       <c r="C7">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D7">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="E7">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G7">
-        <v>434</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B8">
         <v>84</v>
       </c>
       <c r="C8">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D8">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c r="E8">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G8">
-        <v>462</v>
+        <v>547</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B9">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C9">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D9">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="E9">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="F9">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>431</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B10">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="C10">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D10">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="E10">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="F10">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B11">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C11">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="D11">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="E11">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="F11">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="G11">
-        <v>275</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B12">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C12">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="D12">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E12">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="F12">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="G12">
-        <v>294</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B13">
         <v>50</v>
       </c>
       <c r="C13">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D13">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E13">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F13">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G13">
-        <v>311</v>
+        <v>296</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B14">
         <v>53</v>
       </c>
       <c r="C14">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D14">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E14">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F14">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G14">
-        <v>331</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B15">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C15">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="D15">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="E15">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F15">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G15">
-        <v>232</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B16">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C16">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="D16">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="E16">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="F16">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G16">
-        <v>249</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D17">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D18">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E18">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G18">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B19">
+        <v>21</v>
+      </c>
+      <c r="C19">
         <v>17</v>
       </c>
-      <c r="C19">
-        <v>43</v>
-      </c>
       <c r="D19">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E19">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G19">
-        <v>120</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B20">
+        <v>23</v>
+      </c>
+      <c r="C20">
         <v>19</v>
       </c>
-      <c r="C20">
-        <v>46</v>
-      </c>
       <c r="D20">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E20">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F20">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G20">
-        <v>130</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B21">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C21">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D21">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E21">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F21">
         <v>6</v>
       </c>
       <c r="G21">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B22">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C22">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D22">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F22">
         <v>7</v>
       </c>
       <c r="G22">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23">
+        <v>13</v>
+      </c>
+      <c r="D23">
         <v>17</v>
       </c>
-      <c r="C23">
-        <v>29</v>
-      </c>
-      <c r="D23">
-        <v>27</v>
-      </c>
       <c r="E23">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>90</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <v>14</v>
+      </c>
+      <c r="D24">
         <v>19</v>
       </c>
-      <c r="C24">
-        <v>31</v>
-      </c>
-      <c r="D24">
-        <v>29</v>
-      </c>
       <c r="E24">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>98</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C25">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D25">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E25">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F25">
         <v>2</v>
       </c>
       <c r="G25">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B26">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C26">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D26">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F26">
         <v>3</v>
       </c>
       <c r="G26">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>77</v>
@@ -3774,569 +3757,569 @@
         <v>73</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B30">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C30">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="D30">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E30">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="F30">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="G30">
-        <v>442</v>
+        <v>551</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B31">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C31">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="D31">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E31">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F31">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="G31">
-        <v>471</v>
+        <v>587</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B32">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C32">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="D32">
         <v>101</v>
       </c>
       <c r="E32">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F32">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G32">
-        <v>396</v>
+        <v>416</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B33">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C33">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="D33">
         <v>108</v>
       </c>
       <c r="E33">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F33">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G33">
-        <v>422</v>
+        <v>443</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B34">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C34">
+        <v>71</v>
+      </c>
+      <c r="D34">
         <v>108</v>
       </c>
-      <c r="D34">
-        <v>139</v>
-      </c>
       <c r="E34">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F34">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G34">
-        <v>387</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35">
+        <v>42</v>
+      </c>
+      <c r="C35">
+        <v>76</v>
+      </c>
+      <c r="D35">
         <v>115</v>
       </c>
-      <c r="B35">
-        <v>51</v>
-      </c>
-      <c r="C35">
-        <v>115</v>
-      </c>
-      <c r="D35">
-        <v>148</v>
-      </c>
       <c r="E35">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F35">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G35">
-        <v>413</v>
+        <v>313</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B36">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C36">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D36">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E36">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F36">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G36">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B37">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C37">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D37">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E37">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F37">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G37">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B38">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C38">
+        <v>45</v>
+      </c>
+      <c r="D38">
         <v>54</v>
       </c>
-      <c r="D38">
-        <v>76</v>
-      </c>
       <c r="E38">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F38">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G38">
-        <v>218</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B39">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C39">
+        <v>48</v>
+      </c>
+      <c r="D39">
         <v>58</v>
       </c>
-      <c r="D39">
-        <v>81</v>
-      </c>
       <c r="E39">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F39">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G39">
-        <v>233</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B40">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C40">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D40">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E40">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F40">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G40">
-        <v>137</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B41">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C41">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D41">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E41">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F41">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G41">
-        <v>147</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B42">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C42">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D42">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E42">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F42">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G42">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
+        <v>133</v>
+      </c>
+      <c r="B43">
+        <v>27</v>
+      </c>
+      <c r="C43">
+        <v>34</v>
+      </c>
+      <c r="D43">
+        <v>31</v>
+      </c>
+      <c r="E43">
+        <v>29</v>
+      </c>
+      <c r="F43">
+        <v>15</v>
+      </c>
+      <c r="G43">
         <v>136</v>
-      </c>
-      <c r="B43">
-        <v>28</v>
-      </c>
-      <c r="C43">
-        <v>43</v>
-      </c>
-      <c r="D43">
-        <v>39</v>
-      </c>
-      <c r="E43">
-        <v>21</v>
-      </c>
-      <c r="F43">
-        <v>11</v>
-      </c>
-      <c r="G43">
-        <v>142</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B44">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C44">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D44">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E44">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F44">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G44">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B45">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C45">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D45">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="E45">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F45">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G45">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B46">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C46">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D46">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E46">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F46">
         <v>6</v>
       </c>
       <c r="G46">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B47">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C47">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D47">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E47">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F47">
         <v>7</v>
       </c>
       <c r="G47">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B48">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C48">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D48">
+        <v>29</v>
+      </c>
+      <c r="E48">
+        <v>22</v>
+      </c>
+      <c r="F48">
+        <v>8</v>
+      </c>
+      <c r="G48">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49">
+        <v>25</v>
+      </c>
+      <c r="C49">
         <v>32</v>
       </c>
-      <c r="E48">
+      <c r="D49">
+        <v>31</v>
+      </c>
+      <c r="E49">
         <v>24</v>
       </c>
-      <c r="F48">
-        <v>5</v>
-      </c>
-      <c r="G48">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
-      <c r="A49" t="s">
-        <v>125</v>
-      </c>
-      <c r="B49">
+      <c r="F49">
+        <v>9</v>
+      </c>
+      <c r="G49">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" t="s">
+        <v>129</v>
+      </c>
+      <c r="B50">
+        <v>22</v>
+      </c>
+      <c r="C50">
         <v>23</v>
       </c>
-      <c r="C49">
-        <v>43</v>
-      </c>
-      <c r="D49">
-        <v>34</v>
-      </c>
-      <c r="E49">
-        <v>26</v>
-      </c>
-      <c r="F49">
-        <v>6</v>
-      </c>
-      <c r="G49">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" t="s">
-        <v>137</v>
-      </c>
-      <c r="B50">
-        <v>11</v>
-      </c>
-      <c r="C50">
-        <v>21</v>
-      </c>
       <c r="D50">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E50">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F50">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G50">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B51">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C51">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D51">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F51">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G51">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B52">
+        <v>18</v>
+      </c>
+      <c r="C52">
+        <v>25</v>
+      </c>
+      <c r="D52">
+        <v>18</v>
+      </c>
+      <c r="E52">
         <v>10</v>
-      </c>
-      <c r="C52">
-        <v>12</v>
-      </c>
-      <c r="D52">
-        <v>12</v>
-      </c>
-      <c r="E52">
-        <v>7</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B53">
+        <v>20</v>
+      </c>
+      <c r="C53">
+        <v>27</v>
+      </c>
+      <c r="D53">
+        <v>20</v>
+      </c>
+      <c r="E53">
         <v>11</v>
-      </c>
-      <c r="C53">
-        <v>13</v>
-      </c>
-      <c r="D53">
-        <v>13</v>
-      </c>
-      <c r="E53">
-        <v>8</v>
       </c>
       <c r="F53">
         <v>2</v>
       </c>
       <c r="G53">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>79</v>
@@ -4360,778 +4343,703 @@
         <v>85</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="J56" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" t="s">
+        <v>113</v>
+      </c>
+      <c r="B57">
+        <v>43</v>
+      </c>
+      <c r="C57">
+        <v>56</v>
+      </c>
+      <c r="D57">
+        <v>51</v>
+      </c>
+      <c r="E57">
+        <v>59</v>
+      </c>
+      <c r="F57">
+        <v>91</v>
+      </c>
+      <c r="G57">
+        <v>48</v>
+      </c>
+      <c r="H57">
+        <v>61</v>
+      </c>
+      <c r="I57">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58">
+        <v>46</v>
+      </c>
+      <c r="C58">
+        <v>60</v>
+      </c>
+      <c r="D58">
+        <v>55</v>
+      </c>
+      <c r="E58">
+        <v>63</v>
+      </c>
+      <c r="F58">
+        <v>97</v>
+      </c>
+      <c r="G58">
+        <v>51</v>
+      </c>
+      <c r="H58">
+        <v>65</v>
+      </c>
+      <c r="I58">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="57" spans="1:10">
-      <c r="A57" t="s">
+      <c r="B59">
+        <v>59</v>
+      </c>
+      <c r="C59">
+        <v>56</v>
+      </c>
+      <c r="D59">
+        <v>61</v>
+      </c>
+      <c r="E59">
+        <v>72</v>
+      </c>
+      <c r="F59">
+        <v>29</v>
+      </c>
+      <c r="G59">
+        <v>69</v>
+      </c>
+      <c r="H59">
+        <v>59</v>
+      </c>
+      <c r="I59">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60">
+        <v>63</v>
+      </c>
+      <c r="C60">
+        <v>60</v>
+      </c>
+      <c r="D60">
+        <v>65</v>
+      </c>
+      <c r="E60">
+        <v>77</v>
+      </c>
+      <c r="F60">
+        <v>31</v>
+      </c>
+      <c r="G60">
+        <v>74</v>
+      </c>
+      <c r="H60">
+        <v>63</v>
+      </c>
+      <c r="I60">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" t="s">
+        <v>115</v>
+      </c>
+      <c r="B61">
+        <v>51</v>
+      </c>
+      <c r="C61">
+        <v>29</v>
+      </c>
+      <c r="D61">
+        <v>35</v>
+      </c>
+      <c r="E61">
+        <v>56</v>
+      </c>
+      <c r="F61">
+        <v>53</v>
+      </c>
+      <c r="G61">
+        <v>64</v>
+      </c>
+      <c r="H61">
+        <v>80</v>
+      </c>
+      <c r="I61">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" t="s">
+        <v>116</v>
+      </c>
+      <c r="B62">
+        <v>55</v>
+      </c>
+      <c r="C62">
+        <v>31</v>
+      </c>
+      <c r="D62">
+        <v>38</v>
+      </c>
+      <c r="E62">
+        <v>60</v>
+      </c>
+      <c r="F62">
+        <v>57</v>
+      </c>
+      <c r="G62">
+        <v>68</v>
+      </c>
+      <c r="H62">
+        <v>85</v>
+      </c>
+      <c r="I62">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" t="s">
+        <v>132</v>
+      </c>
+      <c r="B63">
+        <v>51</v>
+      </c>
+      <c r="C63">
+        <v>37</v>
+      </c>
+      <c r="D63">
+        <v>59</v>
+      </c>
+      <c r="E63">
+        <v>37</v>
+      </c>
+      <c r="F63">
+        <v>51</v>
+      </c>
+      <c r="G63">
+        <v>56</v>
+      </c>
+      <c r="H63">
+        <v>43</v>
+      </c>
+      <c r="I63">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" t="s">
+        <v>133</v>
+      </c>
+      <c r="B64">
+        <v>55</v>
+      </c>
+      <c r="C64">
+        <v>40</v>
+      </c>
+      <c r="D64">
+        <v>63</v>
+      </c>
+      <c r="E64">
+        <v>40</v>
+      </c>
+      <c r="F64">
+        <v>55</v>
+      </c>
+      <c r="G64">
+        <v>60</v>
+      </c>
+      <c r="H64">
+        <v>46</v>
+      </c>
+      <c r="I64">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" t="s">
+        <v>111</v>
+      </c>
+      <c r="B65">
+        <v>21</v>
+      </c>
+      <c r="C65">
+        <v>37</v>
+      </c>
+      <c r="D65">
+        <v>48</v>
+      </c>
+      <c r="E65">
+        <v>51</v>
+      </c>
+      <c r="F65">
+        <v>45</v>
+      </c>
+      <c r="G65">
+        <v>53</v>
+      </c>
+      <c r="H65">
+        <v>53</v>
+      </c>
+      <c r="I65">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" t="s">
         <v>112</v>
       </c>
-      <c r="B57">
+      <c r="B66">
+        <v>23</v>
+      </c>
+      <c r="C66">
+        <v>40</v>
+      </c>
+      <c r="D66">
+        <v>51</v>
+      </c>
+      <c r="E66">
+        <v>55</v>
+      </c>
+      <c r="F66">
+        <v>48</v>
+      </c>
+      <c r="G66">
+        <v>57</v>
+      </c>
+      <c r="H66">
+        <v>57</v>
+      </c>
+      <c r="I66">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" t="s">
+        <v>125</v>
+      </c>
+      <c r="B67">
+        <v>11</v>
+      </c>
+      <c r="C67">
+        <v>48</v>
+      </c>
+      <c r="D67">
+        <v>56</v>
+      </c>
+      <c r="E67">
+        <v>56</v>
+      </c>
+      <c r="F67">
+        <v>32</v>
+      </c>
+      <c r="G67">
+        <v>45</v>
+      </c>
+      <c r="H67">
+        <v>21</v>
+      </c>
+      <c r="I67">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" t="s">
+        <v>126</v>
+      </c>
+      <c r="B68">
+        <v>12</v>
+      </c>
+      <c r="C68">
+        <v>51</v>
+      </c>
+      <c r="D68">
+        <v>60</v>
+      </c>
+      <c r="E68">
+        <v>60</v>
+      </c>
+      <c r="F68">
+        <v>34</v>
+      </c>
+      <c r="G68">
+        <v>48</v>
+      </c>
+      <c r="H68">
+        <v>23</v>
+      </c>
+      <c r="I68">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" t="s">
+        <v>136</v>
+      </c>
+      <c r="B69">
+        <v>40</v>
+      </c>
+      <c r="C69">
+        <v>29</v>
+      </c>
+      <c r="D69">
+        <v>43</v>
+      </c>
+      <c r="E69">
+        <v>16</v>
+      </c>
+      <c r="F69">
+        <v>35</v>
+      </c>
+      <c r="G69">
+        <v>43</v>
+      </c>
+      <c r="H69">
+        <v>59</v>
+      </c>
+      <c r="I69">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70">
+        <v>43</v>
+      </c>
+      <c r="C70">
+        <v>31</v>
+      </c>
+      <c r="D70">
+        <v>46</v>
+      </c>
+      <c r="E70">
+        <v>17</v>
+      </c>
+      <c r="F70">
+        <v>38</v>
+      </c>
+      <c r="G70">
+        <v>46</v>
+      </c>
+      <c r="H70">
         <v>63</v>
       </c>
-      <c r="C57">
-        <v>65</v>
-      </c>
-      <c r="D57">
-        <v>71</v>
-      </c>
-      <c r="E57">
-        <v>81</v>
-      </c>
-      <c r="F57">
-        <v>55</v>
-      </c>
-      <c r="G57">
-        <v>84</v>
-      </c>
-      <c r="H57">
-        <v>58</v>
-      </c>
-      <c r="I57">
-        <v>11</v>
-      </c>
-      <c r="J57">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
-      <c r="A58" t="s">
-        <v>113</v>
-      </c>
-      <c r="B58">
-        <v>67</v>
-      </c>
-      <c r="C58">
-        <v>69</v>
-      </c>
-      <c r="D58">
-        <v>76</v>
-      </c>
-      <c r="E58">
-        <v>86</v>
-      </c>
-      <c r="F58">
-        <v>59</v>
-      </c>
-      <c r="G58">
-        <v>90</v>
-      </c>
-      <c r="H58">
-        <v>62</v>
-      </c>
-      <c r="I58">
-        <v>12</v>
-      </c>
-      <c r="J58">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59" t="s">
-        <v>114</v>
-      </c>
-      <c r="B59">
-        <v>49</v>
-      </c>
-      <c r="C59">
-        <v>49</v>
-      </c>
-      <c r="D59">
-        <v>52</v>
-      </c>
-      <c r="E59">
-        <v>60</v>
-      </c>
-      <c r="F59">
-        <v>68</v>
-      </c>
-      <c r="G59">
-        <v>80</v>
-      </c>
-      <c r="H59">
-        <v>58</v>
-      </c>
-      <c r="I59">
-        <v>18</v>
-      </c>
-      <c r="J59">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
-      <c r="A60" t="s">
-        <v>115</v>
-      </c>
-      <c r="B60">
-        <v>52</v>
-      </c>
-      <c r="C60">
-        <v>52</v>
-      </c>
-      <c r="D60">
-        <v>56</v>
-      </c>
-      <c r="E60">
-        <v>64</v>
-      </c>
-      <c r="F60">
-        <v>73</v>
-      </c>
-      <c r="G60">
-        <v>85</v>
-      </c>
-      <c r="H60">
-        <v>62</v>
-      </c>
-      <c r="I60">
-        <v>20</v>
-      </c>
-      <c r="J60">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10">
-      <c r="A61" t="s">
-        <v>110</v>
-      </c>
-      <c r="B61">
-        <v>25</v>
-      </c>
-      <c r="C61">
-        <v>42</v>
-      </c>
-      <c r="D61">
-        <v>64</v>
-      </c>
-      <c r="E61">
-        <v>63</v>
-      </c>
-      <c r="F61">
-        <v>63</v>
-      </c>
-      <c r="G61">
-        <v>80</v>
-      </c>
-      <c r="H61">
-        <v>57</v>
-      </c>
-      <c r="I61">
-        <v>10</v>
-      </c>
-      <c r="J61">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
-      <c r="A62" t="s">
-        <v>111</v>
-      </c>
-      <c r="B62">
-        <v>27</v>
-      </c>
-      <c r="C62">
-        <v>45</v>
-      </c>
-      <c r="D62">
-        <v>68</v>
-      </c>
-      <c r="E62">
-        <v>67</v>
-      </c>
-      <c r="F62">
-        <v>67</v>
-      </c>
-      <c r="G62">
-        <v>85</v>
-      </c>
-      <c r="H62">
-        <v>61</v>
-      </c>
-      <c r="I62">
-        <v>11</v>
-      </c>
-      <c r="J62">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
-      <c r="A63" t="s">
-        <v>116</v>
-      </c>
-      <c r="B63">
-        <v>25</v>
-      </c>
-      <c r="C63">
-        <v>33</v>
-      </c>
-      <c r="D63">
-        <v>21</v>
-      </c>
-      <c r="E63">
+      <c r="I70">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" t="s">
+        <v>134</v>
+      </c>
+      <c r="B71">
+        <v>26</v>
+      </c>
+      <c r="C71">
+        <v>8</v>
+      </c>
+      <c r="D71">
         <v>23</v>
       </c>
-      <c r="F63">
-        <v>38</v>
-      </c>
-      <c r="G63">
-        <v>22</v>
-      </c>
-      <c r="H63">
-        <v>20</v>
-      </c>
-      <c r="I63">
-        <v>5</v>
-      </c>
-      <c r="J63">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10">
-      <c r="A64" t="s">
-        <v>117</v>
-      </c>
-      <c r="B64">
-        <v>27</v>
-      </c>
-      <c r="C64">
-        <v>35</v>
-      </c>
-      <c r="D64">
+      <c r="E71">
         <v>23</v>
-      </c>
-      <c r="E64">
-        <v>25</v>
-      </c>
-      <c r="F64">
-        <v>41</v>
-      </c>
-      <c r="G64">
-        <v>24</v>
-      </c>
-      <c r="H64">
-        <v>22</v>
-      </c>
-      <c r="I64">
-        <v>6</v>
-      </c>
-      <c r="J64">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10">
-      <c r="A65" t="s">
-        <v>133</v>
-      </c>
-      <c r="B65">
-        <v>41</v>
-      </c>
-      <c r="C65">
-        <v>36</v>
-      </c>
-      <c r="D65">
-        <v>52</v>
-      </c>
-      <c r="E65">
-        <v>20</v>
-      </c>
-      <c r="F65">
-        <v>27</v>
-      </c>
-      <c r="G65">
-        <v>41</v>
-      </c>
-      <c r="H65">
-        <v>42</v>
-      </c>
-      <c r="I65">
-        <v>12</v>
-      </c>
-      <c r="J65">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10">
-      <c r="A66" t="s">
-        <v>134</v>
-      </c>
-      <c r="B66">
-        <v>44</v>
-      </c>
-      <c r="C66">
-        <v>39</v>
-      </c>
-      <c r="D66">
-        <v>56</v>
-      </c>
-      <c r="E66">
-        <v>22</v>
-      </c>
-      <c r="F66">
-        <v>29</v>
-      </c>
-      <c r="G66">
-        <v>44</v>
-      </c>
-      <c r="H66">
-        <v>45</v>
-      </c>
-      <c r="I66">
-        <v>13</v>
-      </c>
-      <c r="J66">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
-      <c r="A67" t="s">
-        <v>124</v>
-      </c>
-      <c r="B67">
-        <v>14</v>
-      </c>
-      <c r="C67">
-        <v>31</v>
-      </c>
-      <c r="D67">
-        <v>44</v>
-      </c>
-      <c r="E67">
-        <v>42</v>
-      </c>
-      <c r="F67">
-        <v>34</v>
-      </c>
-      <c r="G67">
-        <v>35</v>
-      </c>
-      <c r="H67">
-        <v>18</v>
-      </c>
-      <c r="I67">
-        <v>8</v>
-      </c>
-      <c r="J67">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
-      <c r="A68" t="s">
-        <v>125</v>
-      </c>
-      <c r="B68">
-        <v>15</v>
-      </c>
-      <c r="C68">
-        <v>33</v>
-      </c>
-      <c r="D68">
-        <v>47</v>
-      </c>
-      <c r="E68">
-        <v>45</v>
-      </c>
-      <c r="F68">
-        <v>37</v>
-      </c>
-      <c r="G68">
-        <v>38</v>
-      </c>
-      <c r="H68">
-        <v>20</v>
-      </c>
-      <c r="I68">
-        <v>9</v>
-      </c>
-      <c r="J68">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
-      <c r="A69" t="s">
-        <v>137</v>
-      </c>
-      <c r="B69">
-        <v>21</v>
-      </c>
-      <c r="C69">
-        <v>22</v>
-      </c>
-      <c r="D69">
-        <v>27</v>
-      </c>
-      <c r="E69">
-        <v>17</v>
-      </c>
-      <c r="F69">
-        <v>22</v>
-      </c>
-      <c r="G69">
-        <v>41</v>
-      </c>
-      <c r="H69">
-        <v>35</v>
-      </c>
-      <c r="I69">
-        <v>6</v>
-      </c>
-      <c r="J69">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
-      <c r="A70" t="s">
-        <v>138</v>
-      </c>
-      <c r="B70">
-        <v>23</v>
-      </c>
-      <c r="C70">
-        <v>24</v>
-      </c>
-      <c r="D70">
-        <v>29</v>
-      </c>
-      <c r="E70">
-        <v>19</v>
-      </c>
-      <c r="F70">
-        <v>24</v>
-      </c>
-      <c r="G70">
-        <v>44</v>
-      </c>
-      <c r="H70">
-        <v>38</v>
-      </c>
-      <c r="I70">
-        <v>7</v>
-      </c>
-      <c r="J70">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
-      <c r="A71" t="s">
-        <v>118</v>
-      </c>
-      <c r="B71">
-        <v>29</v>
-      </c>
-      <c r="C71">
-        <v>24</v>
-      </c>
-      <c r="D71">
-        <v>44</v>
-      </c>
-      <c r="E71">
-        <v>18</v>
       </c>
       <c r="F71">
         <v>19</v>
       </c>
       <c r="G71">
+        <v>28</v>
+      </c>
+      <c r="H71">
+        <v>34</v>
+      </c>
+      <c r="I71">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" t="s">
+        <v>135</v>
+      </c>
+      <c r="B72">
+        <v>28</v>
+      </c>
+      <c r="C72">
+        <v>9</v>
+      </c>
+      <c r="D72">
         <v>25</v>
       </c>
-      <c r="H71">
-        <v>30</v>
-      </c>
-      <c r="I71">
-        <v>3</v>
-      </c>
-      <c r="J71">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
-      <c r="A72" t="s">
-        <v>119</v>
-      </c>
-      <c r="B72">
-        <v>31</v>
-      </c>
-      <c r="C72">
-        <v>26</v>
-      </c>
-      <c r="D72">
-        <v>47</v>
-      </c>
       <c r="E72">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F72">
         <v>21</v>
       </c>
       <c r="G72">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H72">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I72">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" t="s">
+        <v>117</v>
+      </c>
+      <c r="B73">
+        <v>31</v>
+      </c>
+      <c r="C73">
+        <v>11</v>
+      </c>
+      <c r="D73">
+        <v>45</v>
+      </c>
+      <c r="E73">
+        <v>11</v>
+      </c>
+      <c r="F73">
+        <v>20</v>
+      </c>
+      <c r="G73">
+        <v>18</v>
+      </c>
+      <c r="H73">
+        <v>31</v>
+      </c>
+      <c r="I73">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" t="s">
+        <v>118</v>
+      </c>
+      <c r="B74">
+        <v>33</v>
+      </c>
+      <c r="C74">
+        <v>12</v>
+      </c>
+      <c r="D74">
+        <v>48</v>
+      </c>
+      <c r="E74">
+        <v>12</v>
+      </c>
+      <c r="F74">
+        <v>22</v>
+      </c>
+      <c r="G74">
+        <v>20</v>
+      </c>
+      <c r="H74">
+        <v>33</v>
+      </c>
+      <c r="I74">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" t="s">
+        <v>129</v>
+      </c>
+      <c r="B75">
+        <v>9</v>
+      </c>
+      <c r="C75">
+        <v>19</v>
+      </c>
+      <c r="D75">
+        <v>23</v>
+      </c>
+      <c r="E75">
+        <v>23</v>
+      </c>
+      <c r="F75">
+        <v>19</v>
+      </c>
+      <c r="G75">
+        <v>16</v>
+      </c>
+      <c r="H75">
+        <v>33</v>
+      </c>
+      <c r="I75">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" t="s">
+        <v>130</v>
+      </c>
+      <c r="B76">
+        <v>10</v>
+      </c>
+      <c r="C76">
+        <v>21</v>
+      </c>
+      <c r="D76">
+        <v>25</v>
+      </c>
+      <c r="E76">
+        <v>25</v>
+      </c>
+      <c r="F76">
+        <v>21</v>
+      </c>
+      <c r="G76">
+        <v>17</v>
+      </c>
+      <c r="H76">
+        <v>35</v>
+      </c>
+      <c r="I76">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" t="s">
+        <v>127</v>
+      </c>
+      <c r="B77">
         <v>4</v>
       </c>
-      <c r="J72">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
-      <c r="A73" t="s">
-        <v>128</v>
-      </c>
-      <c r="B73">
-        <v>14</v>
-      </c>
-      <c r="C73">
-        <v>20</v>
-      </c>
-      <c r="D73">
-        <v>30</v>
-      </c>
-      <c r="E73">
-        <v>34</v>
-      </c>
-      <c r="F73">
-        <v>28</v>
-      </c>
-      <c r="G73">
-        <v>32</v>
-      </c>
-      <c r="H73">
-        <v>21</v>
-      </c>
-      <c r="I73">
-        <v>4</v>
-      </c>
-      <c r="J73">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10">
-      <c r="A74" t="s">
-        <v>129</v>
-      </c>
-      <c r="B74">
-        <v>15</v>
-      </c>
-      <c r="C74">
-        <v>22</v>
-      </c>
-      <c r="D74">
-        <v>32</v>
-      </c>
-      <c r="E74">
-        <v>37</v>
-      </c>
-      <c r="F74">
-        <v>30</v>
-      </c>
-      <c r="G74">
-        <v>34</v>
-      </c>
-      <c r="H74">
-        <v>23</v>
-      </c>
-      <c r="I74">
-        <v>5</v>
-      </c>
-      <c r="J74">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10">
-      <c r="A75" t="s">
-        <v>135</v>
-      </c>
-      <c r="B75">
-        <v>20</v>
-      </c>
-      <c r="C75">
-        <v>9</v>
-      </c>
-      <c r="D75">
-        <v>30</v>
-      </c>
-      <c r="E75">
-        <v>19</v>
-      </c>
-      <c r="F75">
-        <v>14</v>
-      </c>
-      <c r="G75">
-        <v>37</v>
-      </c>
-      <c r="H75">
-        <v>36</v>
-      </c>
-      <c r="I75">
-        <v>3</v>
-      </c>
-      <c r="J75">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10">
-      <c r="A76" t="s">
-        <v>136</v>
-      </c>
-      <c r="B76">
-        <v>22</v>
-      </c>
-      <c r="C76">
-        <v>10</v>
-      </c>
-      <c r="D76">
-        <v>32</v>
-      </c>
-      <c r="E76">
-        <v>21</v>
-      </c>
-      <c r="F76">
-        <v>15</v>
-      </c>
-      <c r="G76">
-        <v>40</v>
-      </c>
-      <c r="H76">
-        <v>39</v>
-      </c>
-      <c r="I76">
-        <v>4</v>
-      </c>
-      <c r="J76">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10">
-      <c r="A77" t="s">
-        <v>120</v>
-      </c>
-      <c r="B77">
+      <c r="C77">
         <v>8</v>
       </c>
-      <c r="C77">
-        <v>12</v>
-      </c>
       <c r="D77">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E77">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F77">
         <v>17</v>
       </c>
       <c r="G77">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H77">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I77">
-        <v>6</v>
-      </c>
-      <c r="J77">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B78">
+        <v>5</v>
+      </c>
+      <c r="C78">
         <v>9</v>
       </c>
-      <c r="C78">
-        <v>13</v>
-      </c>
       <c r="D78">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E78">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F78">
         <v>19</v>
       </c>
       <c r="G78">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H78">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I78">
-        <v>7</v>
-      </c>
-      <c r="J78">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="B79">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C79">
         <v>4</v>
       </c>
       <c r="D79">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E79">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F79">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G79">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H79">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I79">
-        <v>8</v>
-      </c>
-      <c r="J79">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="B80">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C80">
         <v>5</v>
       </c>
       <c r="D80">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E80">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F80">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G80">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H80">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I80">
-        <v>9</v>
-      </c>
-      <c r="J80">
-        <v>100</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -5146,17 +5054,17 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B4" s="5">
         <v>0.2</v>
@@ -5167,7 +5075,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -5196,357 +5104,357 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="E12" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="F12" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B13">
-        <v>500</v>
+        <v>532</v>
       </c>
       <c r="C13">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="D13">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="E13">
-        <v>266</v>
+        <v>283.5</v>
       </c>
       <c r="F13">
-        <v>300</v>
+        <v>319.2</v>
       </c>
       <c r="G13">
-        <v>319.2</v>
+        <v>340.2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B14">
-        <v>434</v>
+        <v>514</v>
       </c>
       <c r="C14">
-        <v>462</v>
+        <v>547</v>
       </c>
       <c r="D14">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="E14">
-        <v>231</v>
+        <v>273.5</v>
       </c>
       <c r="F14">
-        <v>260.4</v>
+        <v>308.4</v>
       </c>
       <c r="G14">
-        <v>277.2</v>
+        <v>328.2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B15">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="C15">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="D15">
-        <v>215.5</v>
+        <v>209.5</v>
       </c>
       <c r="E15">
-        <v>229.5</v>
+        <v>223.5</v>
       </c>
       <c r="F15">
-        <v>258.6</v>
+        <v>251.4</v>
       </c>
       <c r="G15">
-        <v>275.4</v>
+        <v>268.2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B16">
-        <v>275</v>
+        <v>367</v>
       </c>
       <c r="C16">
-        <v>294</v>
+        <v>391</v>
       </c>
       <c r="D16">
-        <v>137.5</v>
+        <v>183.5</v>
       </c>
       <c r="E16">
-        <v>147</v>
+        <v>195.5</v>
       </c>
       <c r="F16">
-        <v>165</v>
+        <v>220.2</v>
       </c>
       <c r="G16">
-        <v>176.4</v>
+        <v>234.6</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B17">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="C17">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="D17">
-        <v>155.5</v>
+        <v>148</v>
       </c>
       <c r="E17">
-        <v>165.5</v>
+        <v>157.5</v>
       </c>
       <c r="F17">
-        <v>186.6</v>
+        <v>177.6</v>
       </c>
       <c r="G17">
-        <v>198.6</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B18">
-        <v>232</v>
+        <v>141</v>
       </c>
       <c r="C18">
-        <v>249</v>
+        <v>152</v>
       </c>
       <c r="D18">
-        <v>116</v>
+        <v>70.5</v>
       </c>
       <c r="E18">
-        <v>124.5</v>
+        <v>76</v>
       </c>
       <c r="F18">
-        <v>139.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G18">
-        <v>149.4</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B19">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C19">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D19">
-        <v>64.5</v>
+        <v>60.5</v>
       </c>
       <c r="E19">
-        <v>69</v>
+        <v>65.5</v>
       </c>
       <c r="F19">
-        <v>77.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="G19">
-        <v>82.8</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B20">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="C20">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="D20">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E20">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="F20">
-        <v>72</v>
+        <v>52.8</v>
       </c>
       <c r="G20">
-        <v>78</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21">
+        <v>90</v>
+      </c>
+      <c r="C21">
         <v>98</v>
       </c>
-      <c r="B21">
-        <v>91</v>
-      </c>
-      <c r="C21">
-        <v>99</v>
-      </c>
       <c r="D21">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="E21">
-        <v>49.5</v>
+        <v>49</v>
       </c>
       <c r="F21">
-        <v>54.6</v>
+        <v>54</v>
       </c>
       <c r="G21">
-        <v>59.4</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B22">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="C22">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="D22">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E22">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="F22">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="G22">
-        <v>58.8</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B23">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C23">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D23">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="E23">
-        <v>21</v>
+        <v>23.5</v>
       </c>
       <c r="F23">
-        <v>22.2</v>
+        <v>25.2</v>
       </c>
       <c r="G23">
-        <v>25.2</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B24" s="11">
         <v>2650</v>
       </c>
       <c r="C24" s="11">
-        <v>2834</v>
+        <v>2837</v>
       </c>
       <c r="D24" s="11">
         <v>1325</v>
       </c>
       <c r="E24" s="11">
-        <v>1417</v>
+        <v>1418.5</v>
       </c>
       <c r="F24" s="11">
         <v>1590</v>
       </c>
       <c r="G24" s="11">
-        <v>1700.4</v>
+        <v>1702.2</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="D27" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="E27" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="F27" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="G27" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B28">
-        <v>442</v>
+        <v>551</v>
       </c>
       <c r="C28">
-        <v>471</v>
+        <v>587</v>
       </c>
       <c r="D28">
-        <v>176.8</v>
+        <v>220.4</v>
       </c>
       <c r="E28">
-        <v>188.4</v>
+        <v>234.8</v>
       </c>
       <c r="F28">
-        <v>212.2</v>
+        <v>264.5</v>
       </c>
       <c r="G28">
-        <v>226.1</v>
+        <v>281.8</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -5554,22 +5462,22 @@
         <v>90</v>
       </c>
       <c r="B29">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="C29">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="D29">
-        <v>158.4</v>
+        <v>166.4</v>
       </c>
       <c r="E29">
-        <v>168.8</v>
+        <v>177.2</v>
       </c>
       <c r="F29">
-        <v>190.1</v>
+        <v>199.7</v>
       </c>
       <c r="G29">
-        <v>202.6</v>
+        <v>212.6</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -5577,160 +5485,160 @@
         <v>92</v>
       </c>
       <c r="B30">
-        <v>387</v>
+        <v>293</v>
       </c>
       <c r="C30">
-        <v>413</v>
+        <v>313</v>
       </c>
       <c r="D30">
-        <v>154.8</v>
+        <v>117.2</v>
       </c>
       <c r="E30">
-        <v>165.2</v>
+        <v>125.2</v>
       </c>
       <c r="F30">
-        <v>185.8</v>
+        <v>140.6</v>
       </c>
       <c r="G30">
-        <v>198.2</v>
+        <v>150.2</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B31">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C31">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D31">
-        <v>100.8</v>
+        <v>101.6</v>
       </c>
       <c r="E31">
-        <v>107.6</v>
+        <v>108.4</v>
       </c>
       <c r="F31">
-        <v>121</v>
+        <v>121.9</v>
       </c>
       <c r="G31">
-        <v>129.1</v>
+        <v>130.1</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B32">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="C32">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="D32">
-        <v>87.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E32">
-        <v>93.2</v>
+        <v>78</v>
       </c>
       <c r="F32">
-        <v>104.6</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="G32">
-        <v>111.8</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B33">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C33">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="D33">
-        <v>54.8</v>
+        <v>48.4</v>
       </c>
       <c r="E33">
-        <v>58.8</v>
+        <v>52.4</v>
       </c>
       <c r="F33">
-        <v>65.8</v>
+        <v>58.1</v>
       </c>
       <c r="G33">
-        <v>70.59999999999999</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B34">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C34">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D34">
-        <v>52.4</v>
+        <v>50.8</v>
       </c>
       <c r="E34">
-        <v>56.8</v>
+        <v>54.4</v>
       </c>
       <c r="F34">
-        <v>62.9</v>
+        <v>61</v>
       </c>
       <c r="G34">
-        <v>68.2</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B35">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C35">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D35">
-        <v>50.4</v>
+        <v>48.4</v>
       </c>
       <c r="E35">
-        <v>54.4</v>
+        <v>52.8</v>
       </c>
       <c r="F35">
-        <v>60.5</v>
+        <v>58.1</v>
       </c>
       <c r="G35">
-        <v>65.3</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B36">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C36">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D36">
-        <v>50</v>
+        <v>49.2</v>
       </c>
       <c r="E36">
-        <v>54</v>
+        <v>53.2</v>
       </c>
       <c r="F36">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G36">
-        <v>64.8</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -5738,119 +5646,119 @@
         <v>97</v>
       </c>
       <c r="B37">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C37">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D37">
-        <v>48.8</v>
+        <v>44.8</v>
       </c>
       <c r="E37">
-        <v>52.8</v>
+        <v>48.4</v>
       </c>
       <c r="F37">
-        <v>58.6</v>
+        <v>53.8</v>
       </c>
       <c r="G37">
-        <v>63.4</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B38">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C38">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D38">
-        <v>28.8</v>
+        <v>31.6</v>
       </c>
       <c r="E38">
-        <v>31.6</v>
+        <v>34.8</v>
       </c>
       <c r="F38">
-        <v>34.6</v>
+        <v>37.9</v>
       </c>
       <c r="G38">
-        <v>37.9</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B39">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="C39">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="D39">
-        <v>16.8</v>
+        <v>28.8</v>
       </c>
       <c r="E39">
-        <v>18.8</v>
+        <v>32</v>
       </c>
       <c r="F39">
-        <v>20.2</v>
+        <v>34.6</v>
       </c>
       <c r="G39">
-        <v>22.6</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B40" s="11">
         <v>2450</v>
       </c>
       <c r="C40" s="11">
-        <v>2626</v>
+        <v>2629</v>
       </c>
       <c r="D40" s="11">
         <v>980</v>
       </c>
       <c r="E40" s="11">
-        <v>1050.4</v>
+        <v>1051.6</v>
       </c>
       <c r="F40" s="11">
         <v>1176</v>
       </c>
       <c r="G40" s="11">
-        <v>1260.5</v>
+        <v>1261.9</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B43" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C43" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="D43" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="E43" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="F43" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="G43" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -5858,114 +5766,114 @@
         <v>91</v>
       </c>
       <c r="B44">
-        <v>488</v>
+        <v>409</v>
       </c>
       <c r="C44">
-        <v>521</v>
+        <v>437</v>
       </c>
       <c r="D44">
-        <v>126.9</v>
+        <v>106.3</v>
       </c>
       <c r="E44">
-        <v>135.5</v>
+        <v>113.6</v>
       </c>
       <c r="F44">
-        <v>152.3</v>
+        <v>127.6</v>
       </c>
       <c r="G44">
-        <v>162.6</v>
+        <v>136.3</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B45">
-        <v>434</v>
+        <v>405</v>
       </c>
       <c r="C45">
-        <v>464</v>
+        <v>433</v>
       </c>
       <c r="D45">
-        <v>112.8</v>
+        <v>105.3</v>
       </c>
       <c r="E45">
-        <v>120.6</v>
+        <v>112.6</v>
       </c>
       <c r="F45">
-        <v>135.4</v>
+        <v>126.4</v>
       </c>
       <c r="G45">
-        <v>144.8</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B46">
-        <v>404</v>
+        <v>368</v>
       </c>
       <c r="C46">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="D46">
-        <v>105</v>
+        <v>95.7</v>
       </c>
       <c r="E46">
-        <v>112.1</v>
+        <v>102.4</v>
       </c>
       <c r="F46">
-        <v>126</v>
+        <v>114.8</v>
       </c>
       <c r="G46">
-        <v>134.5</v>
+        <v>122.9</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B47">
-        <v>187</v>
+        <v>334</v>
       </c>
       <c r="C47">
-        <v>203</v>
+        <v>359</v>
       </c>
       <c r="D47">
-        <v>48.6</v>
+        <v>86.8</v>
       </c>
       <c r="E47">
-        <v>52.8</v>
+        <v>93.3</v>
       </c>
       <c r="F47">
-        <v>58.3</v>
+        <v>104.2</v>
       </c>
       <c r="G47">
-        <v>63.3</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B48">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="C48">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="D48">
-        <v>70.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="E48">
-        <v>75.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F48">
-        <v>84.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="G48">
-        <v>91.09999999999999</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -5973,183 +5881,183 @@
         <v>97</v>
       </c>
       <c r="B49">
-        <v>226</v>
+        <v>269</v>
       </c>
       <c r="C49">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="D49">
-        <v>58.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E49">
-        <v>63.4</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F49">
-        <v>70.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="G49">
-        <v>76.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B50">
-        <v>191</v>
+        <v>265</v>
       </c>
       <c r="C50">
-        <v>208</v>
+        <v>284</v>
       </c>
       <c r="D50">
-        <v>49.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E50">
-        <v>54.1</v>
+        <v>73.8</v>
       </c>
       <c r="F50">
-        <v>59.6</v>
+        <v>82.7</v>
       </c>
       <c r="G50">
-        <v>64.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B51">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="C51">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="D51">
-        <v>49.9</v>
+        <v>41.9</v>
       </c>
       <c r="E51">
-        <v>54.1</v>
+        <v>45.5</v>
       </c>
       <c r="F51">
-        <v>59.9</v>
+        <v>50.2</v>
       </c>
       <c r="G51">
-        <v>64.90000000000001</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B52">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="C52">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="D52">
-        <v>47.6</v>
+        <v>43.4</v>
       </c>
       <c r="E52">
-        <v>51.5</v>
+        <v>46.8</v>
       </c>
       <c r="F52">
-        <v>57.1</v>
+        <v>52.1</v>
       </c>
       <c r="G52">
-        <v>61.8</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B53">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="C53">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="D53">
-        <v>43.7</v>
+        <v>36.9</v>
       </c>
       <c r="E53">
-        <v>47.6</v>
+        <v>40</v>
       </c>
       <c r="F53">
-        <v>52.4</v>
+        <v>44.3</v>
       </c>
       <c r="G53">
-        <v>57.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B54">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="C54">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="D54">
-        <v>30.2</v>
+        <v>19.5</v>
       </c>
       <c r="E54">
-        <v>33.3</v>
+        <v>21.8</v>
       </c>
       <c r="F54">
-        <v>36.2</v>
+        <v>23.4</v>
       </c>
       <c r="G54">
-        <v>39.9</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B55">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="C55">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="D55">
-        <v>23.4</v>
+        <v>12.2</v>
       </c>
       <c r="E55">
-        <v>26</v>
+        <v>13.8</v>
       </c>
       <c r="F55">
-        <v>28.1</v>
+        <v>14.7</v>
       </c>
       <c r="G55">
-        <v>31.2</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B56" s="11">
         <v>2950</v>
       </c>
       <c r="C56" s="11">
-        <v>3180</v>
+        <v>3172</v>
       </c>
       <c r="D56" s="11">
         <v>767</v>
       </c>
       <c r="E56" s="11">
-        <v>826.8</v>
+        <v>824.7</v>
       </c>
       <c r="F56" s="11">
         <v>920.4</v>
       </c>
       <c r="G56" s="11">
-        <v>992.2</v>
+        <v>989.7</v>
       </c>
     </row>
   </sheetData>
@@ -6159,22 +6067,22 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S82"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -6202,80 +6110,80 @@
       </c>
       <c r="K5" s="6"/>
       <c r="L5" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>161</v>
-      </c>
       <c r="E6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>161</v>
-      </c>
       <c r="G6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>161</v>
-      </c>
       <c r="I6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="J6" s="6" t="s">
-        <v>161</v>
-      </c>
       <c r="K6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="M6" s="6"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B7">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C7">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D7">
+        <v>151</v>
+      </c>
+      <c r="E7">
+        <v>164</v>
+      </c>
+      <c r="F7">
         <v>161</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>171</v>
       </c>
-      <c r="F7">
-        <v>158</v>
-      </c>
-      <c r="G7">
-        <v>169</v>
-      </c>
       <c r="H7">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="I7">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="J7">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="K7">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="L7">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -6283,37 +6191,37 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C8">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D8">
+        <v>125</v>
+      </c>
+      <c r="E8">
         <v>134</v>
       </c>
-      <c r="E8">
+      <c r="F8">
+        <v>133</v>
+      </c>
+      <c r="G8">
         <v>142</v>
       </c>
-      <c r="F8">
-        <v>132</v>
-      </c>
-      <c r="G8">
-        <v>141</v>
-      </c>
       <c r="H8">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I8">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="J8">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K8">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L8">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6321,34 +6229,34 @@
         <v>24</v>
       </c>
       <c r="B9">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C9">
         <v>46</v>
       </c>
       <c r="D9">
+        <v>77</v>
+      </c>
+      <c r="E9">
         <v>80</v>
       </c>
-      <c r="E9">
-        <v>86</v>
-      </c>
       <c r="F9">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G9">
         <v>85</v>
       </c>
       <c r="H9">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I9">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J9">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K9">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L9">
         <v>266</v>
@@ -6356,230 +6264,230 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B10">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C10">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D10">
+        <v>81</v>
+      </c>
+      <c r="E10">
         <v>86</v>
       </c>
-      <c r="E10">
-        <v>90</v>
-      </c>
       <c r="F10">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G10">
         <v>91</v>
       </c>
       <c r="H10">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="I10">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J10">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K10">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L10">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11">
         <v>5</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11">
         <v>9</v>
       </c>
       <c r="G11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I11">
         <v>5</v>
       </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>2</v>
       </c>
-      <c r="K11">
-        <v>3</v>
-      </c>
       <c r="L11">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B12">
         <v>23</v>
       </c>
       <c r="C12">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D12">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E12">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F12">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G12">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H12">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I12">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J12">
+        <v>8</v>
+      </c>
+      <c r="K12">
         <v>11</v>
       </c>
-      <c r="K12">
-        <v>13</v>
-      </c>
       <c r="L12">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C13">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D13">
+        <v>125</v>
+      </c>
+      <c r="E13">
+        <v>134</v>
+      </c>
+      <c r="F13">
         <v>132</v>
-      </c>
-      <c r="E13">
-        <v>140</v>
-      </c>
-      <c r="F13">
-        <v>130</v>
       </c>
       <c r="G13">
         <v>140</v>
       </c>
       <c r="H13">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I13">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J13">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K13">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L13">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E14">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F14">
         <v>82</v>
       </c>
       <c r="G14">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H14">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I14">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="J14">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K14">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L14">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B15">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C15">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E15">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F15">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G15">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H15">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="I15">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J15">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K15">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L15">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -6587,34 +6495,34 @@
         <v>75</v>
       </c>
       <c r="B16" s="4">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="C16" s="4">
-        <v>461</v>
+        <v>483</v>
       </c>
       <c r="D16" s="4">
+        <v>758</v>
+      </c>
+      <c r="E16" s="4">
+        <v>810</v>
+      </c>
+      <c r="F16" s="4">
         <v>801</v>
       </c>
-      <c r="E16" s="4">
-        <v>854</v>
-      </c>
-      <c r="F16" s="4">
-        <v>796</v>
-      </c>
       <c r="G16" s="4">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="H16" s="4">
-        <v>417</v>
+        <v>478</v>
       </c>
       <c r="I16" s="4">
-        <v>447</v>
+        <v>511</v>
       </c>
       <c r="J16" s="4">
-        <v>207</v>
+        <v>162</v>
       </c>
       <c r="K16" s="4">
-        <v>224</v>
+        <v>177</v>
       </c>
       <c r="L16" s="4">
         <v>2650</v>
@@ -6622,7 +6530,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -6630,18 +6538,18 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B20">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C20">
         <v>197.5</v>
@@ -6652,7 +6560,7 @@
         <v>22</v>
       </c>
       <c r="B21">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C21">
         <v>163.6</v>
@@ -6671,10 +6579,10 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B23">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C23">
         <v>104.5</v>
@@ -6682,10 +6590,10 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B24">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C24">
         <v>12</v>
@@ -6693,10 +6601,10 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B25">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C25">
         <v>48.6</v>
@@ -6704,10 +6612,10 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B26">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C26">
         <v>163.6</v>
@@ -6715,10 +6623,10 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B27">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C27">
         <v>100.6</v>
@@ -6726,10 +6634,10 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B28">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C28">
         <v>98.8</v>
@@ -6737,7 +6645,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -6765,80 +6673,80 @@
       </c>
       <c r="K32" s="6"/>
       <c r="L32" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>161</v>
-      </c>
       <c r="E33" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F33" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="F33" s="6" t="s">
-        <v>161</v>
-      </c>
       <c r="G33" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H33" s="6" t="s">
-        <v>161</v>
-      </c>
       <c r="I33" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J33" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="J33" s="6" t="s">
-        <v>161</v>
-      </c>
       <c r="K33" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="M33" s="6"/>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B34">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C34">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D34">
+        <v>128</v>
+      </c>
+      <c r="E34">
+        <v>137</v>
+      </c>
+      <c r="F34">
         <v>133</v>
       </c>
-      <c r="E34">
+      <c r="G34">
         <v>142</v>
       </c>
-      <c r="F34">
-        <v>135</v>
-      </c>
-      <c r="G34">
-        <v>144</v>
-      </c>
       <c r="H34">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I34">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J34">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K34">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L34">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -6846,37 +6754,37 @@
         <v>22</v>
       </c>
       <c r="B35">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C35">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D35">
+        <v>106</v>
+      </c>
+      <c r="E35">
+        <v>111</v>
+      </c>
+      <c r="F35">
         <v>108</v>
       </c>
-      <c r="E35">
-        <v>117</v>
-      </c>
-      <c r="F35">
-        <v>110</v>
-      </c>
       <c r="G35">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H35">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I35">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J35">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K35">
         <v>27</v>
       </c>
       <c r="L35">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -6884,34 +6792,34 @@
         <v>24</v>
       </c>
       <c r="B36">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C36">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D36">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E36">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F36">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G36">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H36">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I36">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J36">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K36">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L36">
         <v>248</v>
@@ -6919,75 +6827,75 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B37">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C37">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D37">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E37">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F37">
+        <v>75</v>
+      </c>
+      <c r="G37">
         <v>80</v>
-      </c>
-      <c r="G37">
-        <v>85</v>
       </c>
       <c r="H37">
         <v>52</v>
       </c>
       <c r="I37">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J37">
+        <v>19</v>
+      </c>
+      <c r="K37">
         <v>21</v>
       </c>
-      <c r="K37">
-        <v>22</v>
-      </c>
       <c r="L37">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D38">
+        <v>6</v>
+      </c>
+      <c r="E38">
+        <v>9</v>
+      </c>
+      <c r="F38">
         <v>7</v>
       </c>
-      <c r="E38">
-        <v>6</v>
-      </c>
-      <c r="F38">
-        <v>6</v>
-      </c>
       <c r="G38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H38">
         <v>3</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38">
         <v>20</v>
@@ -6995,142 +6903,142 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B39">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C39">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D39">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E39">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F39">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G39">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H39">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I39">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J39">
+        <v>12</v>
+      </c>
+      <c r="K39">
         <v>13</v>
       </c>
-      <c r="K39">
-        <v>14</v>
-      </c>
       <c r="L39">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B40">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C40">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D40">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E40">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F40">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G40">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H40">
         <v>72</v>
       </c>
       <c r="I40">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J40">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K40">
         <v>26</v>
       </c>
       <c r="L40">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B41">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C41">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D41">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E41">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F41">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G41">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H41">
         <v>50</v>
       </c>
       <c r="I41">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J41">
         <v>18</v>
       </c>
       <c r="K41">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L41">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B42">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C42">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D42">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E42">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F42">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G42">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H42">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I42">
         <v>47</v>
@@ -7139,10 +7047,10 @@
         <v>14</v>
       </c>
       <c r="K42">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L42">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -7150,22 +7058,22 @@
         <v>75</v>
       </c>
       <c r="B43" s="4">
-        <v>412</v>
+        <v>459</v>
       </c>
       <c r="C43" s="4">
-        <v>442</v>
+        <v>493</v>
       </c>
       <c r="D43" s="4">
-        <v>699</v>
+        <v>675</v>
       </c>
       <c r="E43" s="4">
-        <v>748</v>
+        <v>721</v>
       </c>
       <c r="F43" s="4">
-        <v>710</v>
+        <v>690</v>
       </c>
       <c r="G43" s="4">
-        <v>758</v>
+        <v>739</v>
       </c>
       <c r="H43" s="4">
         <v>466</v>
@@ -7174,10 +7082,10 @@
         <v>500</v>
       </c>
       <c r="J43" s="4">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K43" s="4">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L43" s="4">
         <v>2450</v>
@@ -7185,7 +7093,7 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -7193,18 +7101,18 @@
         <v>17</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B47">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C47">
         <v>132</v>
@@ -7215,13 +7123,13 @@
         <v>22</v>
       </c>
       <c r="B48">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C48">
         <v>106.4</v>
       </c>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:17">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -7232,20 +7140,20 @@
         <v>71.59999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:17">
       <c r="A50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B50">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C50">
         <v>75.40000000000001</v>
       </c>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:17">
       <c r="A51" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B51">
         <v>20</v>
@@ -7254,56 +7162,56 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:17">
       <c r="A52" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B52">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C52">
         <v>54.6</v>
       </c>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:17">
       <c r="A53" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B53">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C53">
         <v>106.4</v>
       </c>
     </row>
-    <row r="54" spans="1:19">
+    <row r="54" spans="1:17">
       <c r="A54" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B54">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C54">
         <v>73.09999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:17">
       <c r="A55" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B55">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C55">
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:17">
       <c r="A58" s="3" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17">
       <c r="A59" s="6" t="s">
         <v>17</v>
       </c>
@@ -7336,243 +7244,215 @@
       </c>
       <c r="O59" s="6"/>
       <c r="P59" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q59" s="6"/>
-      <c r="R59" s="6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D60" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="E60" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="O60" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P60" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q60" s="6"/>
+    </row>
+    <row r="61" spans="1:17">
+      <c r="A61" t="s">
         <v>161</v>
       </c>
-      <c r="E60" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="J60" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="K60" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="L60" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="M60" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="N60" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="O60" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q60" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="R60" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="S60" s="6"/>
-    </row>
-    <row r="61" spans="1:19">
-      <c r="A61" t="s">
-        <v>162</v>
-      </c>
       <c r="B61">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C61">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D61">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E61">
         <v>68</v>
       </c>
       <c r="F61">
+        <v>84</v>
+      </c>
+      <c r="G61">
+        <v>92</v>
+      </c>
+      <c r="H61">
+        <v>78</v>
+      </c>
+      <c r="I61">
+        <v>84</v>
+      </c>
+      <c r="J61">
+        <v>74</v>
+      </c>
+      <c r="K61">
         <v>82</v>
       </c>
-      <c r="G61">
-        <v>87</v>
-      </c>
-      <c r="H61">
-        <v>75</v>
-      </c>
-      <c r="I61">
-        <v>83</v>
-      </c>
-      <c r="J61">
-        <v>71</v>
-      </c>
-      <c r="K61">
-        <v>77</v>
-      </c>
       <c r="L61">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M61">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="N61">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="O61">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="P61">
-        <v>17</v>
-      </c>
-      <c r="Q61">
-        <v>21</v>
-      </c>
-      <c r="R61">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17">
       <c r="A62" t="s">
         <v>22</v>
       </c>
       <c r="B62">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C62">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D62">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E62">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F62">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G62">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H62">
         <v>71</v>
       </c>
       <c r="I62">
+        <v>77</v>
+      </c>
+      <c r="J62">
+        <v>69</v>
+      </c>
+      <c r="K62">
         <v>76</v>
       </c>
-      <c r="J62">
-        <v>67</v>
-      </c>
-      <c r="K62">
-        <v>72</v>
-      </c>
       <c r="L62">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="M62">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="N62">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="O62">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="P62">
-        <v>17</v>
-      </c>
-      <c r="Q62">
-        <v>17</v>
-      </c>
-      <c r="R62">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17">
       <c r="A63" t="s">
         <v>24</v>
       </c>
       <c r="B63">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C63">
+        <v>55</v>
+      </c>
+      <c r="D63">
         <v>48</v>
       </c>
-      <c r="D63">
-        <v>50</v>
-      </c>
       <c r="E63">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F63">
+        <v>66</v>
+      </c>
+      <c r="G63">
+        <v>73</v>
+      </c>
+      <c r="H63">
+        <v>58</v>
+      </c>
+      <c r="I63">
+        <v>68</v>
+      </c>
+      <c r="J63">
+        <v>60</v>
+      </c>
+      <c r="K63">
         <v>65</v>
       </c>
-      <c r="G63">
+      <c r="L63">
+        <v>67</v>
+      </c>
+      <c r="M63">
         <v>72</v>
       </c>
-      <c r="H63">
-        <v>61</v>
-      </c>
-      <c r="I63">
-        <v>66</v>
-      </c>
-      <c r="J63">
-        <v>58</v>
-      </c>
-      <c r="K63">
-        <v>62</v>
-      </c>
-      <c r="L63">
-        <v>78</v>
-      </c>
-      <c r="M63">
-        <v>84</v>
-      </c>
       <c r="N63">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="O63">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="P63">
-        <v>13</v>
-      </c>
-      <c r="Q63">
-        <v>16</v>
-      </c>
-      <c r="R63">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17">
       <c r="A64" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B64">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C64">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D64">
         <v>31</v>
@@ -7587,110 +7467,98 @@
         <v>44</v>
       </c>
       <c r="H64">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I64">
+        <v>39</v>
+      </c>
+      <c r="J64">
+        <v>39</v>
+      </c>
+      <c r="K64">
         <v>41</v>
       </c>
-      <c r="J64">
-        <v>34</v>
-      </c>
-      <c r="K64">
-        <v>37</v>
-      </c>
       <c r="L64">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M64">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N64">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="O64">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="P64">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16">
+      <c r="A65" t="s">
+        <v>163</v>
+      </c>
+      <c r="B65">
         <v>6</v>
       </c>
-      <c r="Q64">
-        <v>9</v>
-      </c>
-      <c r="R64">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18">
-      <c r="A65" t="s">
+      <c r="C65">
+        <v>7</v>
+      </c>
+      <c r="D65">
+        <v>5</v>
+      </c>
+      <c r="E65">
+        <v>5</v>
+      </c>
+      <c r="F65">
+        <v>10</v>
+      </c>
+      <c r="G65">
+        <v>8</v>
+      </c>
+      <c r="H65">
+        <v>8</v>
+      </c>
+      <c r="I65">
+        <v>6</v>
+      </c>
+      <c r="J65">
+        <v>5</v>
+      </c>
+      <c r="K65">
+        <v>5</v>
+      </c>
+      <c r="L65">
+        <v>7</v>
+      </c>
+      <c r="M65">
+        <v>8</v>
+      </c>
+      <c r="N65">
+        <v>7</v>
+      </c>
+      <c r="O65">
+        <v>10</v>
+      </c>
+      <c r="P65">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
+      <c r="A66" t="s">
         <v>164</v>
       </c>
-      <c r="B65">
-        <v>3</v>
-      </c>
-      <c r="C65">
-        <v>4</v>
-      </c>
-      <c r="D65">
-        <v>6</v>
-      </c>
-      <c r="E65">
-        <v>8</v>
-      </c>
-      <c r="F65">
-        <v>6</v>
-      </c>
-      <c r="G65">
-        <v>7</v>
-      </c>
-      <c r="H65">
-        <v>5</v>
-      </c>
-      <c r="I65">
-        <v>5</v>
-      </c>
-      <c r="J65">
-        <v>4</v>
-      </c>
-      <c r="K65">
-        <v>6</v>
-      </c>
-      <c r="L65">
-        <v>8</v>
-      </c>
-      <c r="M65">
-        <v>9</v>
-      </c>
-      <c r="N65">
-        <v>6</v>
-      </c>
-      <c r="O65">
-        <v>7</v>
-      </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>0</v>
-      </c>
-      <c r="R65">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18">
-      <c r="A66" t="s">
-        <v>165</v>
-      </c>
       <c r="B66">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C66">
         <v>19</v>
       </c>
       <c r="D66">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E66">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F66">
         <v>24</v>
@@ -7699,166 +7567,148 @@
         <v>25</v>
       </c>
       <c r="H66">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I66">
+        <v>24</v>
+      </c>
+      <c r="J66">
+        <v>22</v>
+      </c>
+      <c r="K66">
+        <v>24</v>
+      </c>
+      <c r="L66">
         <v>23</v>
       </c>
-      <c r="J66">
-        <v>21</v>
-      </c>
-      <c r="K66">
-        <v>23</v>
-      </c>
-      <c r="L66">
+      <c r="M66">
         <v>27</v>
       </c>
-      <c r="M66">
-        <v>29</v>
-      </c>
       <c r="N66">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O66">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P66">
-        <v>6</v>
-      </c>
-      <c r="Q66">
-        <v>6</v>
-      </c>
-      <c r="R66">
         <v>155</v>
       </c>
     </row>
-    <row r="67" spans="1:18">
+    <row r="67" spans="1:16">
       <c r="A67" t="s">
+        <v>165</v>
+      </c>
+      <c r="B67">
+        <v>56</v>
+      </c>
+      <c r="C67">
+        <v>62</v>
+      </c>
+      <c r="D67">
+        <v>56</v>
+      </c>
+      <c r="E67">
+        <v>58</v>
+      </c>
+      <c r="F67">
+        <v>76</v>
+      </c>
+      <c r="G67">
+        <v>82</v>
+      </c>
+      <c r="H67">
+        <v>71</v>
+      </c>
+      <c r="I67">
+        <v>75</v>
+      </c>
+      <c r="J67">
+        <v>68</v>
+      </c>
+      <c r="K67">
+        <v>73</v>
+      </c>
+      <c r="L67">
+        <v>76</v>
+      </c>
+      <c r="M67">
+        <v>82</v>
+      </c>
+      <c r="N67">
+        <v>79</v>
+      </c>
+      <c r="O67">
+        <v>84</v>
+      </c>
+      <c r="P67">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
+      <c r="A68" t="s">
         <v>166</v>
-      </c>
-      <c r="B67">
-        <v>50</v>
-      </c>
-      <c r="C67">
-        <v>57</v>
-      </c>
-      <c r="D67">
-        <v>57</v>
-      </c>
-      <c r="E67">
-        <v>59</v>
-      </c>
-      <c r="F67">
-        <v>74</v>
-      </c>
-      <c r="G67">
-        <v>80</v>
-      </c>
-      <c r="H67">
-        <v>69</v>
-      </c>
-      <c r="I67">
-        <v>73</v>
-      </c>
-      <c r="J67">
-        <v>66</v>
-      </c>
-      <c r="K67">
-        <v>71</v>
-      </c>
-      <c r="L67">
-        <v>88</v>
-      </c>
-      <c r="M67">
-        <v>93</v>
-      </c>
-      <c r="N67">
-        <v>65</v>
-      </c>
-      <c r="O67">
-        <v>68</v>
-      </c>
-      <c r="P67">
-        <v>16</v>
-      </c>
-      <c r="Q67">
-        <v>17</v>
-      </c>
-      <c r="R67">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18">
-      <c r="A68" t="s">
-        <v>167</v>
       </c>
       <c r="B68">
         <v>34</v>
       </c>
       <c r="C68">
+        <v>36</v>
+      </c>
+      <c r="D68">
+        <v>36</v>
+      </c>
+      <c r="E68">
+        <v>37</v>
+      </c>
+      <c r="F68">
+        <v>46</v>
+      </c>
+      <c r="G68">
+        <v>49</v>
+      </c>
+      <c r="H68">
+        <v>43</v>
+      </c>
+      <c r="I68">
+        <v>46</v>
+      </c>
+      <c r="J68">
+        <v>41</v>
+      </c>
+      <c r="K68">
+        <v>44</v>
+      </c>
+      <c r="L68">
+        <v>47</v>
+      </c>
+      <c r="M68">
+        <v>50</v>
+      </c>
+      <c r="N68">
+        <v>46</v>
+      </c>
+      <c r="O68">
+        <v>49</v>
+      </c>
+      <c r="P68">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16">
+      <c r="A69" t="s">
+        <v>167</v>
+      </c>
+      <c r="B69">
         <v>32</v>
       </c>
-      <c r="D68">
-        <v>32</v>
-      </c>
-      <c r="E68">
-        <v>36</v>
-      </c>
-      <c r="F68">
-        <v>44</v>
-      </c>
-      <c r="G68">
-        <v>50</v>
-      </c>
-      <c r="H68">
-        <v>42</v>
-      </c>
-      <c r="I68">
-        <v>44</v>
-      </c>
-      <c r="J68">
-        <v>40</v>
-      </c>
-      <c r="K68">
-        <v>41</v>
-      </c>
-      <c r="L68">
-        <v>52</v>
-      </c>
-      <c r="M68">
-        <v>55</v>
-      </c>
-      <c r="N68">
-        <v>39</v>
-      </c>
-      <c r="O68">
-        <v>41</v>
-      </c>
-      <c r="P68">
-        <v>10</v>
-      </c>
-      <c r="Q68">
-        <v>11</v>
-      </c>
-      <c r="R68">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18">
-      <c r="A69" t="s">
-        <v>168</v>
-      </c>
-      <c r="B69">
-        <v>29</v>
-      </c>
       <c r="C69">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D69">
         <v>31</v>
       </c>
       <c r="E69">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F69">
         <v>42</v>
@@ -7867,169 +7717,157 @@
         <v>44</v>
       </c>
       <c r="H69">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I69">
         <v>41</v>
       </c>
       <c r="J69">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K69">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L69">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="M69">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="N69">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="O69">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="P69">
-        <v>9</v>
-      </c>
-      <c r="Q69">
-        <v>10</v>
-      </c>
-      <c r="R69">
         <v>269</v>
       </c>
     </row>
-    <row r="70" spans="1:18">
+    <row r="70" spans="1:16">
       <c r="A70" s="4" t="s">
         <v>75</v>
       </c>
       <c r="B70" s="4">
-        <v>316</v>
+        <v>350</v>
       </c>
       <c r="C70" s="4">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="D70" s="4">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E70" s="4">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="F70" s="4">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="G70" s="4">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="H70" s="4">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="I70" s="4">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="J70" s="4">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="K70" s="4">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="L70" s="4">
-        <v>528</v>
+        <v>468</v>
       </c>
       <c r="M70" s="4">
-        <v>566</v>
+        <v>502</v>
       </c>
       <c r="N70" s="4">
-        <v>393</v>
+        <v>478</v>
       </c>
       <c r="O70" s="4">
-        <v>424</v>
+        <v>512</v>
       </c>
       <c r="P70" s="4">
-        <v>94</v>
-      </c>
-      <c r="Q70" s="4">
-        <v>107</v>
-      </c>
-      <c r="R70" s="4">
         <v>2950</v>
       </c>
     </row>
-    <row r="72" spans="1:18">
+    <row r="72" spans="1:16">
       <c r="A72" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16">
       <c r="A73" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16">
       <c r="A74" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B74">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C74">
         <v>112.6</v>
       </c>
     </row>
-    <row r="75" spans="1:18">
+    <row r="75" spans="1:16">
       <c r="A75" t="s">
         <v>22</v>
       </c>
       <c r="B75">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C75">
         <v>102.8</v>
       </c>
     </row>
-    <row r="76" spans="1:18">
+    <row r="76" spans="1:16">
       <c r="A76" t="s">
         <v>24</v>
       </c>
       <c r="B76">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="C76">
         <v>90</v>
       </c>
     </row>
-    <row r="77" spans="1:18">
+    <row r="77" spans="1:16">
       <c r="A77" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B77">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C77">
         <v>55</v>
       </c>
     </row>
-    <row r="78" spans="1:18">
+    <row r="78" spans="1:16">
       <c r="A78" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B78">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C78">
         <v>9.800000000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:18">
+    <row r="79" spans="1:16">
       <c r="A79" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B79">
         <v>155</v>
@@ -8038,12 +7876,12 @@
         <v>33.3</v>
       </c>
     </row>
-    <row r="80" spans="1:18">
+    <row r="80" spans="1:16">
       <c r="A80" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B80">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C80">
         <v>102.8</v>
@@ -8051,7 +7889,7 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B81">
         <v>293</v>
@@ -8062,7 +7900,7 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B82">
         <v>269</v>
@@ -8086,122 +7924,122 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
